--- a/artfynd/A 16948-2024 artfynd.xlsx
+++ b/artfynd/A 16948-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117571874</v>
+        <v>117571981</v>
       </c>
       <c r="B2" t="n">
         <v>97836</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571401</v>
+        <v>571202</v>
       </c>
       <c r="R2" t="n">
-        <v>6419940</v>
+        <v>6420135</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117571842</v>
+        <v>117571874</v>
       </c>
       <c r="B3" t="n">
-        <v>57303</v>
+        <v>97836</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +802,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571386</v>
+        <v>571401</v>
       </c>
       <c r="R3" t="n">
-        <v>6419952</v>
+        <v>6419940</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,17 +880,13 @@
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117571981</v>
+        <v>117571963</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
+        <v>90519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,39 +917,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571202</v>
+        <v>571173</v>
       </c>
       <c r="R4" t="n">
-        <v>6420135</v>
+        <v>6420127</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,6 +992,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Nytt rekord i samma tall!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117571963</v>
+        <v>117571842</v>
       </c>
       <c r="B5" t="n">
-        <v>90519</v>
+        <v>57303</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,34 +1040,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1071,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571173</v>
+        <v>571386</v>
       </c>
       <c r="R5" t="n">
-        <v>6420127</v>
+        <v>6419952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1112,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Nytt rekord i samma tall!</t>
+          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,7 +1121,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16948-2024 artfynd.xlsx
+++ b/artfynd/A 16948-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117571981</v>
+        <v>117571842</v>
       </c>
       <c r="B2" t="n">
-        <v>97836</v>
+        <v>57304</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571202</v>
+        <v>571386</v>
       </c>
       <c r="R2" t="n">
-        <v>6420135</v>
+        <v>6419952</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,13 +761,17 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,7 +793,7 @@
         <v>117571874</v>
       </c>
       <c r="B3" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>117571963</v>
       </c>
       <c r="B4" t="n">
-        <v>90519</v>
+        <v>90521</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117571842</v>
+        <v>117571981</v>
       </c>
       <c r="B5" t="n">
-        <v>57303</v>
+        <v>97838</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,35 +1036,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571386</v>
+        <v>571202</v>
       </c>
       <c r="R5" t="n">
-        <v>6419952</v>
+        <v>6420135</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,17 +1114,13 @@
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16948-2024 artfynd.xlsx
+++ b/artfynd/A 16948-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117571842</v>
+        <v>117571963</v>
       </c>
       <c r="B2" t="n">
-        <v>57304</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571386</v>
+        <v>571173</v>
       </c>
       <c r="R2" t="n">
-        <v>6419952</v>
+        <v>6420127</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +761,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Bearbetat stubbe</t>
+          <t>Nytt rekord i samma tall!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,51 +789,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117571874</v>
+        <v>117571842</v>
       </c>
       <c r="B3" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571401</v>
+        <v>571386</v>
       </c>
       <c r="R3" t="n">
-        <v>6419940</v>
+        <v>6419952</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,13 +870,17 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117571981</v>
+        <v>117571855</v>
       </c>
       <c r="B4" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,11 +927,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -957,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571202</v>
+        <v>571408</v>
       </c>
       <c r="R4" t="n">
-        <v>6420135</v>
+        <v>6419923</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,50 +1005,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117571963</v>
+        <v>117571874</v>
       </c>
       <c r="B5" t="n">
-        <v>90521</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1071,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571173</v>
+        <v>571401</v>
       </c>
       <c r="R5" t="n">
-        <v>6420127</v>
+        <v>6419940</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,11 +1090,6 @@
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Nytt rekord i samma tall!</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1136,6 +1112,116 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>117571981</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 16948, ÅBo, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>571202</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6420135</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
